--- a/claimit_shops_template.xlsx
+++ b/claimit_shops_template.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -451,14 +451,11 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="8" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="42" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
-    <col width="16" customWidth="1" min="17" max="17"/>
-    <col width="11" customWidth="1" min="18" max="18"/>
-    <col width="11" customWidth="1" min="19" max="19"/>
-    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="42" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -524,46 +521,31 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>has_rewards</t>
+          <t>about</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>has_redeem</t>
+          <t>timing</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>about</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>timing</t>
+          <t>lat</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>lat</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
           <t>lng</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>image</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="60" customHeight="1">
+    </row>
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Indian Mart</t>
@@ -620,98 +602,26 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>Indian Mart is your one-stop neighbourhood store in Padi, offering fresh groceries, daily essentials, and household items.</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Daily: 8am – 9pm</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Indian Mart is your one-stop neighbourhood store in Padi, offering fresh groceries, daily essentials, and household items.</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>Daily: 8am – 9pm</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
           <t>+91 44 2651 1234</t>
         </is>
       </c>
-      <c r="R2" s="2" t="n">
+      <c r="P2" s="2" t="n">
         <v>13.1197</v>
       </c>
-      <c r="S2" s="2" t="n">
+      <c r="Q2" s="2" t="n">
         <v>80.2183</v>
       </c>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>↙ paste photo into this cell</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="60" customHeight="1"/>
-    <row r="4" ht="60" customHeight="1"/>
-    <row r="5" ht="60" customHeight="1"/>
-    <row r="6" ht="60" customHeight="1"/>
-    <row r="7" ht="60" customHeight="1"/>
-    <row r="8" ht="60" customHeight="1"/>
-    <row r="9" ht="60" customHeight="1"/>
-    <row r="10" ht="60" customHeight="1"/>
-    <row r="11" ht="60" customHeight="1"/>
-    <row r="12" ht="60" customHeight="1"/>
-    <row r="13" ht="60" customHeight="1"/>
-    <row r="14" ht="60" customHeight="1"/>
-    <row r="15" ht="60" customHeight="1"/>
-    <row r="16" ht="60" customHeight="1"/>
-    <row r="17" ht="60" customHeight="1"/>
-    <row r="18" ht="60" customHeight="1"/>
-    <row r="19" ht="60" customHeight="1"/>
-    <row r="20" ht="60" customHeight="1"/>
-    <row r="21" ht="60" customHeight="1"/>
-    <row r="22" ht="60" customHeight="1"/>
-    <row r="23" ht="60" customHeight="1"/>
-    <row r="24" ht="60" customHeight="1"/>
-    <row r="25" ht="60" customHeight="1"/>
-    <row r="26" ht="60" customHeight="1"/>
-    <row r="27" ht="60" customHeight="1"/>
-    <row r="28" ht="60" customHeight="1"/>
-    <row r="29" ht="60" customHeight="1"/>
-    <row r="30" ht="60" customHeight="1"/>
-    <row r="31" ht="60" customHeight="1"/>
-    <row r="32" ht="60" customHeight="1"/>
-    <row r="33" ht="60" customHeight="1"/>
-    <row r="34" ht="60" customHeight="1"/>
-    <row r="35" ht="60" customHeight="1"/>
-    <row r="36" ht="60" customHeight="1"/>
-    <row r="37" ht="60" customHeight="1"/>
-    <row r="38" ht="60" customHeight="1"/>
-    <row r="39" ht="60" customHeight="1"/>
-    <row r="40" ht="60" customHeight="1"/>
-    <row r="41" ht="60" customHeight="1"/>
-    <row r="42" ht="60" customHeight="1"/>
-    <row r="43" ht="60" customHeight="1"/>
-    <row r="44" ht="60" customHeight="1"/>
-    <row r="45" ht="60" customHeight="1"/>
-    <row r="46" ht="60" customHeight="1"/>
-    <row r="47" ht="60" customHeight="1"/>
-    <row r="48" ht="60" customHeight="1"/>
-    <row r="49" ht="60" customHeight="1"/>
-    <row r="50" ht="60" customHeight="1"/>
-    <row r="51" ht="60" customHeight="1"/>
-    <row r="52" ht="60" customHeight="1"/>
-    <row r="53" ht="60" customHeight="1"/>
-    <row r="54" ht="60" customHeight="1"/>
-    <row r="55" ht="60" customHeight="1"/>
-    <row r="56" ht="60" customHeight="1"/>
-    <row r="57" ht="60" customHeight="1"/>
-    <row r="58" ht="60" customHeight="1"/>
-    <row r="59" ht="60" customHeight="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -723,7 +633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A45"/>
+  <dimension ref="A1:A44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -789,253 +699,246 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5. has_rewards / has_redeem: type TRUE or FALSE.</t>
+          <t>5. lat / lng: optional map coordinates (leave blank if unknown).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6. lat / lng: optional map coordinates (leave blank if unknown).</t>
+          <t>6. No image column: each shop shows a random image from its category — upload those</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>7. image: click a cell in the image column → Insert → Picture, and place the shop</t>
+          <t xml:space="preserve">   on Admin → Category Images. Redeem/Reward is chosen later in shop registration.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   photo over that row. Leave blank to use a placeholder (add a photo later in admin).</t>
+          <t>7. Save the file and upload it in Admin → Bulk Upload Shops.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>8. Save the file and upload it in Admin → Bulk Upload Shops.</t>
-        </is>
-      </c>
+      <c r="A13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Valid category names (type these in the 'categories' column)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Valid category names (type these in the 'categories' column)</t>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>New deals</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>New deals</t>
+          <t>Groceries</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Groceries</t>
+          <t>Supermarket</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Supermarket</t>
+          <t>Pharmacy</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Pharmacy</t>
+          <t>Salon</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Salon</t>
+          <t>Gym</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gym</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Restaurant</t>
+          <t>Cafes</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Cafes</t>
+          <t>Clothing</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Department</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>Electronics</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Books</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Books</t>
+          <t>Toys</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Toys</t>
+          <t>Baby</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Baby</t>
+          <t>Home Decor</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Home Decor</t>
+          <t>Furniture</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Furniture</t>
+          <t>Spa</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Spa</t>
+          <t>Schools</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Schools</t>
+          <t>Colleges</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Colleges</t>
+          <t>Tutoring</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Tutoring</t>
+          <t>Clinics</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Clinics</t>
+          <t>Hospitals</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Hospitals</t>
+          <t>Pets</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Pets</t>
+          <t>Sports</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Travel</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Mobile &amp; Accessories</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Mobile &amp; Accessories</t>
+          <t>Computer &amp; Laptop</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Computer &amp; Laptop</t>
+          <t>Gifts</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Gifts</t>
+          <t>Jewellery</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
-        <is>
-          <t>Jewellery</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
         <is>
           <t>Shoes</t>
         </is>
